--- a/data/outputs/Library_Catalog_Report.xlsx
+++ b/data/outputs/Library_Catalog_Report.xlsx
@@ -456,14 +456,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="56" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="176" customWidth="1" min="5" max="5"/>
+    <col width="177" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1894,6 +1894,881 @@
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>OL17732W</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Bible</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>OL2745568A</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Bible, Religion, Bibles, Theology, Scripture</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:01:32</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1200s</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>OL66554W</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Pride And Prejudice</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1813</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>OL21594A</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Fiction, Romance, Historical, Regency, British and Irish fiction (fictional works by one author), Brothers and sisters, Courtship, Drama</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:01:32</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1810s</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>OL138052W</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Alices Adventures In Wonderland</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1865</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>OL22098A</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Alice (fictitious character : carroll), fiction, British and irish fiction (fictional works by one author), Fiction, fantasy, general, JUVENILE FICTION, classics</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:01:32</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1860s</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>OL8193416W</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>The Picture Of Dorian Gray</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1890</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>OL20646A</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>British and irish fiction (fictional works by one author), Conduct of life, fiction, Fantasy fiction, Appearance (Philosophy), Fiction</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:01:32</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1890s</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>OL53908W</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Adventures Of Huckleberry Finn</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1876</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>OL18319A</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>adventure and adventurers, Adventure stories, American fiction (fictional works by one author), American literature, Boys</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:01:32</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1870s</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>OL455305W</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>The Scarlet Letter</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>OL26681A</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Fiction, Puritans, Puritans in fiction, History, Adultery in fiction</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:01:32</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1800s</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>OL45089W</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Robinson Crusoe</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1686</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>OL18283A</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Crusoe, robinson (fictitious character), fiction, British and irish fiction (fictional works by one author), Survival, Fiction, Dans la littérature</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:01:32</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1680s</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>OL8193478W</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Oliver Twist</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1822</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>OL24638A</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Bildungsromans, Boys, Brigands and robbers, British and irish fiction (fictional works by one author), British fiction</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:01:32</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1820s</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>OL66562W</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Sense And Sensibility</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1811</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>OL21594A</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Fiction, Romance, Historical, Regency, Inheritance and succession, fiction, Mate selection, fiction, Social classes, fiction, Family life, fiction</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:01:32</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1810s</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>OL8193465W</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>A Tale Of Two Cities</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>OL24638A</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>British, British and irish fiction (fictional works by one author), Children's fiction, Criticism and interpretation, English fiction</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:01:32</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1800s</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>OL1089297W</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>The Prince</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>1515</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>OL23135A</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Political science, early works to 1800, Machiavel, Nicolas, 1469-1527. Prince, Classic Literature, Fiction, Ouvrages avant 1800</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1510s</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>OL66544W</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Persuasion</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1789</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>OL21594A</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Fiction, Romance, Historical, Regency, Love stories, English, Moški in ženske, V leposlovju, Medosebni odnosi</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1780s</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>OL102749W</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Moby Dick</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>1851</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>OL29497A</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>American Sea stories, Mentally ill, Whaling, Science Fiction &amp; Fantasy, Whales</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1850s</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>OL8193387W</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Hard Times</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>1854</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>OL24638A</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Fiction, Social problems, Utilitarianism, Education, Social life and customs</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1850s</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>OL2772007W</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>The Yellow Wallpaper</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>1892</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>OL408063A</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Literature, Special collections, Cynthia Hilden, Married women, Psychology</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1890s</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>OL8193406W</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>The Mayor Of Casterbridge</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>OL18277A</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>British and irish fiction (fictional works by one author), Wessex (england), fiction, Fathers and daughters, fiction, Long Now Manual for Civilization, Fiction, psychological</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1800s</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>OL43024W</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>As A Man Thinketh</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>OL9777A</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>New Thought, Conduct of life, Miniature books, Specimens, Inspirational</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1900s</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>OL86318W</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Ulysses</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1914</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>OL31827A</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Married people, Male friendship, Fiction, Historical Fiction, Psychological fiction</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1910s</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>OL76399W</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Saint Francis Of Assisi</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>1923</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>OL18524A</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Biography &amp; Autobiography, Nonfiction, Philosophy, Religion &amp; Spirituality, Francis, of assisi, saint, 1182-1226</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1920s</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>OL151515W</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>La Poetica</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>1479</v>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>OL22105A</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Metaphysics, Early works to 1800, Metaphysica (Aristoteles), Rhetoric, ancient, Ethics, greece</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1470s</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>OL1244914W</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Princesse De Cleves</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>1678</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>OL948700A</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Fiction, History, Married women, Nobility, Princesse de Cleves (La Fayette, Madame de)</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1670s</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>OL176086W</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Basil</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>1852</v>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>OL22358A</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Fiction, Fathers and sons, Young men, Revenge, Inheritance and succession</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1850s</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>OL10432709W</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Братья Карамазовы</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>OL22242A</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Literature - Classics / Criticism, Russian, Literature: Classics, Classics, Literary</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1880s</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>OL15692719W</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Der Antichrist</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>OL20157A</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Christianity, Controversial literature, Antichrist, Christianity, controversial literature, Philosophy</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1890s</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>OL65430W</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>The Awakening</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>1899</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>OL35183A</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Adultery, American literature, Classic Literature, Criticism and interpretation, feminist fiction</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13 16:02:53</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1890s</t>
         </is>
       </c>
     </row>
@@ -1908,7 +2783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1958,193 +2833,193 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>OL411267A</t>
+          <t>OL24638A</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1996</v>
+        <v>1800</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1999</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>OL1521655A</t>
+          <t>OL411267A</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2002</v>
+        <v>1996</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2002</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>OL158239A</t>
+          <t>OL21594A</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1985</v>
+        <v>1789</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2001</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>OL6815485A</t>
+          <t>OL1521655A</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2009</v>
+        <v>2002</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2011</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>OL1283561A</t>
+          <t>OL6815485A</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>OL104A</t>
+          <t>OL158239A</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2025</v>
+        <v>1985</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2025</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>OL101A</t>
+          <t>OL1283561A</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2008</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>OL1071215A</t>
+          <t>OL105A</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1983</v>
+        <v>2019</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1983</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>OL106A</t>
+          <t>OL104A</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2009</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>OL105A</t>
+          <t>OL103A</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2019</v>
+        <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2019</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>OL107A</t>
+          <t>OL102A</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v/>
+        <v>1999</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v/>
+        <v>1999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>OL1143170A</t>
+          <t>OL106A</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1973</v>
+        <v>2009</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1973</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="15">
@@ -2166,289 +3041,625 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>OL102A</t>
+          <t>OL18277A</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1999</v>
+        <v>1800</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1999</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>OL103A</t>
+          <t>OL18283A</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v/>
+        <v>1686</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v/>
+        <v>1686</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>OL25278A</t>
+          <t>OL18319A</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2013</v>
+        <v>1876</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2013</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>OL2123356A</t>
+          <t>OL107A</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1841</v>
+        <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1841</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>OL3853673A</t>
+          <t>OL1071215A</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2013</v>
+        <v>1983</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2013</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>OL259932A</t>
+          <t>OL1143170A</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>2000</v>
+        <v>1973</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2000</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>OL3871440A</t>
+          <t>OL101A</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>OL4194836A</t>
+          <t>OL2123356A</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>2018</v>
+        <v>1841</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2018</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>OL466123A</t>
+          <t>OL20646A</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2013</v>
+        <v>1890</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2013</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>OL32997A</t>
+          <t>OL20157A</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1994</v>
+        <v>1895</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1994</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>OL5372765A</t>
+          <t>OL18524A</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>2005</v>
+        <v>1923</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2005</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>OL6867889A</t>
+          <t>OL22242A</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>2010</v>
+        <v>1880</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2010</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>OL6887918A</t>
+          <t>OL22358A</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>2011</v>
+        <v>1852</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2011</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>OL722147A</t>
+          <t>OL22105A</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1990</v>
+        <v>1479</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1990</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>OL7244458A</t>
+          <t>OL22098A</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>2015</v>
+        <v>1865</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2015</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>OL7309633A</t>
+          <t>OL259932A</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>2012</v>
+        <v>2000</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2012</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>OL773995A</t>
+          <t>OL26681A</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>2008</v>
+        <v>1800</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2008</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>OL2745568A</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>OL29497A</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1851</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>OL31827A</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1914</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>OL32997A</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>OL23135A</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1515</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>OL25278A</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>OL3853673A</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>OL35183A</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>1899</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>OL408063A</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1892</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>OL3871440A</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>OL4194836A</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>OL466123A</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>OL5372765A</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>OL6867889A</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>OL6887918A</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>OL722147A</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1990</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>OL7244458A</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>OL7309633A</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>OL773995A</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>OL7955380A</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="2" t="n">
+      <c r="B52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="2" t="n">
         <v>2013</v>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D52" s="2" t="n">
         <v>2013</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>OL948700A</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1678</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>OL9777A</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>1902</v>
       </c>
     </row>
   </sheetData>
@@ -2472,7 +3683,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>OLICAS Catalog Key Performance Indicators</t>
+          <t>Library Catalog Key Performance Indicators</t>
         </is>
       </c>
     </row>
@@ -2495,7 +3706,7 @@
         </is>
       </c>
       <c r="B4" s="5">
-        <f>COUNTA('Catalog Overview'!A2:A41)</f>
+        <f>COUNTA('Catalog Overview'!A2:A66)</f>
         <v/>
       </c>
     </row>
@@ -2506,7 +3717,7 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTA('Author Analytics'!A2:A33)</f>
+        <f>COUNTA('Author Analytics'!A2:A54)</f>
         <v/>
       </c>
     </row>
@@ -2517,7 +3728,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>AVERAGE('Catalog Overview'!C2:C41)</f>
+        <f>AVERAGE('Catalog Overview'!C2:C66)</f>
         <v/>
       </c>
     </row>
@@ -2528,7 +3739,7 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>MIN('Catalog Overview'!C2:C41)</f>
+        <f>MIN('Catalog Overview'!C2:C66)</f>
         <v/>
       </c>
     </row>
@@ -2539,7 +3750,7 @@
         </is>
       </c>
       <c r="B8" s="5">
-        <f>MAX('Catalog Overview'!C2:C41)</f>
+        <f>MAX('Catalog Overview'!C2:C66)</f>
         <v/>
       </c>
     </row>
